--- a/artfynd/A 32394-2026 artfynd.xlsx
+++ b/artfynd/A 32394-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136009461</v>
       </c>
       <c r="B2" t="n">
-        <v>92316</v>
+        <v>92319</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136009577</v>
       </c>
       <c r="B3" t="n">
-        <v>92123</v>
+        <v>92126</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32394-2026 artfynd.xlsx
+++ b/artfynd/A 32394-2026 artfynd.xlsx
@@ -1030,7 +1030,7 @@
         <v>136391206</v>
       </c>
       <c r="B5" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>136391254</v>
       </c>
       <c r="B6" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
